--- a/artfynd/A 59643-2019 artfynd.xlsx
+++ b/artfynd/A 59643-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59643-2019 artfynd.xlsx
+++ b/artfynd/A 59643-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,132 +790,6 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>86555849</v>
-      </c>
-      <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Furudal NO om (*knärot* /stjälk/), Srm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>643482.504643206</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6572438.474191077</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Södertälje</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Ytterenhörna</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>AB-Söd-0263</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2018-10-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2018-10-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Obs: Flera dellokaler. Se privata obsar! Sandviken, S om, Obskoord: 6572979/1597637/5 m ().</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
